--- a/data/trans_bre/P1419-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1419-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>11,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>153,64%</t>
+          <t>169,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 14,92</t>
+          <t>9,85; 14,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,2</t>
+          <t>10,13; 14,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,73</t>
+          <t>6,8; 11,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 13,68</t>
+          <t>8,44; 14,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>158,46; 352,15</t>
+          <t>157,43; 353,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>304,2; 959,73</t>
+          <t>307,83; 959,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>194,2; 685,4</t>
+          <t>180,64; 705,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,72; 249,35</t>
+          <t>96,29; 270,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>174,49%</t>
+          <t>173,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,05</t>
+          <t>3,19; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,59</t>
+          <t>3,22; 5,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,31</t>
+          <t>1,99; 4,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,9</t>
+          <t>4,84; 7,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,52; 391,72</t>
+          <t>119,27; 389,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>251,19; 1095,31</t>
+          <t>276,98; 1025,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>113,91; 457,08</t>
+          <t>109,45; 418,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,48; 305,66</t>
+          <t>118,55; 258,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>176,52%</t>
+          <t>164,44%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,02</t>
+          <t>1,46; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,57</t>
+          <t>1,02; 4,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,76</t>
+          <t>-0,03; 3,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,76</t>
+          <t>2,32; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,78; 529,98</t>
+          <t>40,88; 490,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 823,37</t>
+          <t>-23,82; 691,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,82; 370,69</t>
+          <t>60,94; 332,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>184,49%</t>
+          <t>183,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,01</t>
+          <t>6,55; 9,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,33</t>
+          <t>6,23; 8,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,59</t>
+          <t>3,74; 5,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,72</t>
+          <t>6,07; 8,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>192,27; 355,19</t>
+          <t>181,26; 357,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>390,3; 928,07</t>
+          <t>413,86; 961,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>197,09; 437,69</t>
+          <t>193,16; 445,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>121,51; 261,18</t>
+          <t>139,08; 238,42</t>
         </is>
       </c>
     </row>
